--- a/imatrix_input_excel_headers/OPG_Purchase_Headers.xlsx
+++ b/imatrix_input_excel_headers/OPG_Purchase_Headers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IMT290\Desktop\Projects\po-OPG\OPG_input_excel_headers\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IMT290\Desktop\Projects\po-OPG\imatrix_input_excel_headers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4A37A18-B663-4715-9DF0-5C7B3EB9176D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B0F9CC-CAB2-4432-92E3-0C3EEC80981A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{C87FA182-E24E-45DD-BFA0-28A5687A41B2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" xr2:uid="{C87FA182-E24E-45DD-BFA0-28A5687A41B2}"/>
   </bookViews>
   <sheets>
     <sheet name="OPG_Purchase_headers" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="128">
   <si>
     <t>Company Code</t>
   </si>
@@ -433,7 +433,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -451,6 +451,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -524,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -584,6 +590,7 @@
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2769,7 +2776,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{842C9403-9B7B-41EA-A623-441A2584CB84}">
-  <dimension ref="A1:Z2"/>
+  <dimension ref="A1:AA2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
@@ -2777,30 +2784,31 @@
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="16.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="20" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" s="20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>1</v>
       </c>
@@ -2816,71 +2824,74 @@
       <c r="E1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="H1" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="H1" s="20" t="s">
+      <c r="I1" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="I1" s="20" t="s">
+      <c r="J1" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="J1" s="20" t="s">
+      <c r="K1" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="L1" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="L1" s="20" t="s">
+      <c r="M1" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>114</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="20" t="s">
+      <c r="S1" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="S1" s="20" t="s">
+      <c r="T1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="20" t="s">
+      <c r="U1" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="U1" s="20" t="s">
+      <c r="V1" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="V1" s="20" t="s">
+      <c r="W1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="W1" s="20" t="s">
+      <c r="X1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="X1" s="20" t="s">
+      <c r="Y1" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="20" t="s">
+      <c r="Z1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="20" t="s">
+      <c r="AA1" s="20" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -2896,67 +2907,67 @@
       <c r="E2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>75</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>118</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>119</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>120</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>121</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>122</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>123</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>124</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>66</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>83</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>125</v>
       </c>
-      <c r="Q2" t="s">
-        <v>72</v>
-      </c>
       <c r="R2" t="s">
+        <v>72</v>
+      </c>
+      <c r="S2" t="s">
         <v>76</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>126</v>
       </c>
-      <c r="T2">
+      <c r="U2">
         <v>4</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>77</v>
       </c>
-      <c r="V2">
+      <c r="W2">
         <v>19200</v>
       </c>
-      <c r="W2">
+      <c r="X2">
         <v>3456</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>127</v>
       </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>1</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>72</v>
       </c>
     </row>
